--- a/data/pedidos_2026-08-10.xlsx
+++ b/data/pedidos_2026-08-10.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,17 +521,14 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>alcaldía de La Paz este en el centro comercial el encuentro</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Alcaldía de La Paz Este | El Encuentro Zacatecoluca</t>
-        </is>
-      </c>
+          <t xml:space="preserve">alcaldía de La Paz este en el centro comercial el encuentro
+</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>seiko fondo negro</t>
+          <t>seiko 5 fondo negro</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -591,14 +588,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Municipio de San Luis la Herradura, Cantón Los Blancos, La Paz Centro.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>A la par del Centro Escolar Católico y del Centro Recreativo Coopas</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Cantón Los Blancos, La Paz Centro. A la par del Centro Escolar Católico y del Centro Recreativo Coopas
+</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>Seiko 5 fondo negro</t>
@@ -637,6 +631,356 @@
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3. Eduardo Granados</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>61374356</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>La Libertad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>SANTA TECLA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>17 av sur, 14 calle oriente</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>empresa, DISZASA, redondel Utila</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Casio F105</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar a la entrega</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4. juan Carlos cortez ramirez</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>70998674</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Sonsonate</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>SONZACATE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>urbanización el sauce, polígono j4 casa 11</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>punto de referencia media cuadra arriba de restaurante wosushi</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>old money plata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar a la entrega</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5. Kathya Fiorella Angel Martinez</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>75972586</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>San Salvador</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ILOPANGO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Cimas de San Bartolo 1, pasaje 21, casa 1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>frente a Iglesia Ministerio Belen</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2 wood negro (2x1)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar a la entrega</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6. Julian requeno</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>75419698</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CONCHAGUA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>la union, conchagua, llano los patos</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>frente a tienda erika</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Casio mtp1101 dorado</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>25.00</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar a la entrega</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7. Lucía Margarita Ángel Aguilera</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>70534440</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>San Salvador</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TONACATEPEQUE</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Urbanización Altos de las Flores II</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sin referencia</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Classic plata fondo Negro + Grabado: Feliz vida, mi vida te amo</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>17.50</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Contactar al cliente para coordinar a la entrega</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/pedidos_2026-08-10.xlsx
+++ b/data/pedidos_2026-08-10.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pedidos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Pedidos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -560,7 +560,7 @@
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="P2" t="inlineStr"/>
@@ -627,7 +627,7 @@
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="P3" t="inlineStr"/>
@@ -697,7 +697,7 @@
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="P4" t="inlineStr"/>
@@ -767,7 +767,7 @@
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="P5" t="inlineStr"/>
@@ -837,7 +837,7 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
@@ -907,7 +907,7 @@
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="P7" t="inlineStr"/>
@@ -977,7 +977,7 @@
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>success</t>
         </is>
       </c>
       <c r="P8" t="inlineStr"/>

--- a/data/pedidos_2026-08-10.xlsx
+++ b/data/pedidos_2026-08-10.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,45 +454,35 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Grabado (Si/No)</t>
+          <t>Precio total</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Mensaje del grabado</t>
+          <t>Pagado (Si/No)</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Precio total</t>
+          <t>Fecha de entrega</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Pagado (Si/No)</t>
+          <t>Observaciones</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Fecha de entrega</t>
+          <t>Numero de emergencia</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Observaciones</t>
+          <t>Estado subida</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
-        <is>
-          <t>Numero de emergencia</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>Estado subida</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
@@ -521,49 +511,46 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">alcaldía de La Paz este en el centro comercial el encuentro
-</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>alcaldía de La Paz este en el centro comercial el encuentro</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>centro comercial el encuentro</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>seiko 5 fondo negro</t>
+          <t>seiko fondo negro</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
+          <t>Cambio!!! cliente entrega cambio</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Cambio!!! cliente entrega cambio</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -588,11 +575,14 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cantón Los Blancos, La Paz Centro. A la par del Centro Escolar Católico y del Centro Recreativo Coopas
-</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
+          <t>Cantón Los Blancos. A la par del Centro Escolar Católico y del Centro Recreativo Coopas</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>A la par del Centro Escolar Católico y del Centro Recreativo Coopas</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Seiko 5 fondo negro</t>
@@ -600,37 +590,31 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Contactar al cliente para coordinar a la entrega</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -655,12 +639,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>17 av sur, 14 calle oriente</t>
+          <t>17 av sur, 14 calle oriente, empresa DISZASA, redondel Utila</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>empresa, DISZASA, redondel Utila</t>
+          <t>empresa DISZASA, redondel Utila</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -670,37 +654,31 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Contactar al cliente para coordinar a la entrega</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -730,7 +708,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>punto de referencia media cuadra arriba de restaurante wosushi</t>
+          <t>media cuadra arriba de restaurante wosushi sonzacate</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -740,37 +718,31 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Contactar al cliente para coordinar a la entrega</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -805,42 +777,36 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2 wood negro (2x1)</t>
+          <t>2x1; 2 - wood negro</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Contactar al cliente para coordinar a la entrega</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -855,7 +821,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>La Unión</t>
+          <t>La Union</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -865,7 +831,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>la union, conchagua, llano los patos</t>
+          <t>llano los patos, frente a tienda erika</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -880,37 +846,31 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
-          <t>25.00</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
+          <t>Contactar al cliente para coordinar la entrega</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Contactar al cliente para coordinar a la entrega</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -945,42 +905,36 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Classic plata fondo Negro + Grabado: Feliz vida, mi vida te amo</t>
+          <t>Classic plata fondo Negro</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>17.50</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>17.50</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
+          <t>Envío Gratis</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Contactar al cliente para coordinar a la entrega</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>success</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
